--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487965_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487965_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8403</v>
+        <v>6.755</v>
       </c>
       <c r="E2" t="n">
-        <v>7.522</v>
+        <v>6.6052</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3183</v>
+        <v>0.1498</v>
       </c>
       <c r="G2" t="n">
         <v>2.7196</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4221</v>
+        <v>0.3368</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1014</v>
+        <v>0.1846</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3207</v>
+        <v>0.1522</v>
       </c>
       <c r="V2" t="n">
         <v>4.4914</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8011</v>
+        <v>2.6802</v>
       </c>
       <c r="E3" t="n">
-        <v>2.499</v>
+        <v>2.052</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3021</v>
+        <v>0.6282</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6516999999999999</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7987</v>
+        <v>-0.3222</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1103</v>
+        <v>-0.3366</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6884</v>
+        <v>0.0145</v>
       </c>
       <c r="V3" t="n">
         <v>1.4737</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8323</v>
+        <v>2.2326</v>
       </c>
       <c r="E4" t="n">
-        <v>2.302</v>
+        <v>2.5057</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4696</v>
+        <v>-0.2731</v>
       </c>
       <c r="G4" t="n">
         <v>2.2849</v>
@@ -766,13 +766,13 @@
         <v>0.3964</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8491</v>
+        <v>-0.4488</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.301</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5481</v>
+        <v>-0.3515</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. LASCORZ RIVARES</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6202</v>
+        <v>-0.1546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2676</v>
+        <v>-0.0709</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8878</v>
+        <v>-0.0837</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8343</v>
+        <v>0.2005</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1723</v>
+        <v>0.5984</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.662</v>
+        <v>-0.3979</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0876</v>
+        <v>2.5213</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0876</v>
+        <v>2.6704</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.149</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-2.3208</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2599</v>
+        <v>-2.0719</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.662</v>
+        <v>-0.2488</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>-1.784</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5788</v>
+        <v>-0.7892</v>
       </c>
       <c r="T7" t="n">
-        <v>0.18</v>
+        <v>-0.489</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7588</v>
+        <v>-0.3002</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.218</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.3479</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MARKOTA</t>
+          <t>F. LASCORZ RIVARES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9348</v>
+        <v>-0.6773</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9468</v>
+        <v>0.1262</v>
       </c>
       <c r="F8" t="n">
-        <v>0.012</v>
+        <v>-0.8036</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.585</v>
+        <v>-0.8343</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0876</v>
+        <v>-0.1723</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4974</v>
+        <v>-0.662</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3907</v>
+        <v>0.0876</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7087</v>
+        <v>0.0876</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3181</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9757</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7964</v>
+        <v>-0.2599</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8207</v>
+        <v>-0.662</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5203</v>
+        <v>-0.636</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6129</v>
+        <v>0.0386</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1333</v>
+        <v>-0.6746</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>M. FERNANDEZ GIL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0352</v>
+        <v>-1.0359</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6427</v>
+        <v>-3.2387</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3926</v>
+        <v>2.2028</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2005</v>
+        <v>0.0129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5984</v>
+        <v>-0.9016</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3979</v>
+        <v>0.9145</v>
       </c>
       <c r="J9" t="n">
-        <v>2.5213</v>
+        <v>0.1251</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6704</v>
+        <v>0.1614</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.149</v>
+        <v>-0.0363</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3208</v>
+        <v>-0.1123</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0719</v>
+        <v>-1.0631</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2488</v>
+        <v>0.9508</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.784</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R9" t="n">
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6698</v>
+        <v>-0.4213</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0608</v>
+        <v>-0.1991</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.609</v>
+        <v>-0.2222</v>
       </c>
       <c r="V9" t="n">
-        <v>2.218</v>
+        <v>2.1476</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8701</v>
+        <v>0.7997</v>
       </c>
       <c r="X9" t="n">
         <v>1.3479</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ GIL</t>
+          <t>P. MARKOTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3062</v>
+        <v>-1.2864</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3406</v>
+        <v>-0.6807</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0343</v>
+        <v>-0.6057</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0129</v>
+        <v>-0.585</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9016</v>
+        <v>-0.0876</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9145</v>
+        <v>-0.4974</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1251</v>
+        <v>0.3907</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1614</v>
+        <v>1.7087</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0363</v>
+        <v>-1.3181</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1123</v>
+        <v>-0.9757</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0631</v>
+        <v>-1.7964</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9508</v>
+        <v>0.8207</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7751</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6916</v>
+        <v>0.1687</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.301</v>
+        <v>-0.3468</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3907</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1476</v>
+        <v>-0.8701</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7997</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>1.3479</v>
+        <v>-1.1367</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4188</v>
+        <v>-1.3345</v>
       </c>
       <c r="E11" t="n">
         <v>-0.127</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2917</v>
+        <v>-1.2075</v>
       </c>
       <c r="G11" t="n">
         <v>-1.486</v>
@@ -1312,13 +1312,13 @@
         <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3293</v>
+        <v>-0.245</v>
       </c>
       <c r="T11" t="n">
         <v>-0.1138</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. AGUERA ZEA</t>
+          <t>P. LOPEZ GOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.3911</v>
+        <v>-5.5779</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.957</v>
+        <v>-3.6131</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4341</v>
+        <v>-1.9648</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0808</v>
+        <v>-4.4458</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1422</v>
+        <v>-2.8234</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.223</v>
+        <v>-1.6224</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.237</v>
+        <v>-2.125</v>
       </c>
       <c r="K12" t="n">
-        <v>2.0783</v>
+        <v>-0.8873</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.3153</v>
+        <v>-1.2377</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8438</v>
+        <v>-2.3208</v>
       </c>
       <c r="N12" t="n">
         <v>-1.9361</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0923</v>
+        <v>-0.3847</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0348</v>
+        <v>-0.7268</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7377</v>
+        <v>-0.4266</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2971</v>
+        <v>-0.3002</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.6808</v>
+        <v>-0.6036</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.0704</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.6808</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. LOPEZ GOMEZ</t>
+          <t>J. AGUERA ZEA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4585</v>
+        <v>-5.9803</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1849</v>
+        <v>-3.8551</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2736</v>
+        <v>-2.1252</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.4458</v>
+        <v>-2.0808</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8234</v>
+        <v>0.1422</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.6224</v>
+        <v>-2.223</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.125</v>
+        <v>-1.237</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8873</v>
+        <v>2.0783</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2377</v>
+        <v>-3.3153</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.3208</v>
+        <v>-0.8438</v>
       </c>
       <c r="N13" t="n">
         <v>-1.9361</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3847</v>
+        <v>1.0923</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1982</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6074</v>
+        <v>-0.6241</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9984</v>
+        <v>-0.6359</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.609</v>
+        <v>0.0118</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.6036</v>
+        <v>-2.6808</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0704</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5331</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.483099999999998</v>
+        <v>-3.171099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5996000000000006</v>
+        <v>0.9115999999999991</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.0827</v>
+        <v>-4.0828</v>
       </c>
       <c r="G14" t="n">
         <v>-3.6577</v>
@@ -1525,7 +1525,7 @@
         <v>13.3471</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.839300000000001</v>
+        <v>-4.8393</v>
       </c>
       <c r="M14" t="n">
         <v>-12.1654</v>
@@ -1537,7 +1537,7 @@
         <v>3.5098</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.9823</v>
+        <v>-1.982300000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.8755</v>
@@ -1546,13 +1546,13 @@
         <v>11.8933</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.0197</v>
+        <v>-3.7079</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.7339</v>
+        <v>-2.4218</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2858</v>
+        <v>-1.2859</v>
       </c>
       <c r="V14" t="n">
         <v>6.1762</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.473</v>
+        <v>4.0177</v>
       </c>
       <c r="E15" t="n">
-        <v>7.2155</v>
+        <v>4.8725</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7426</v>
+        <v>-0.8549</v>
       </c>
       <c r="G15" t="n">
         <v>2.5298</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4367</v>
+        <v>1.9814</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5684</v>
+        <v>1.2254</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8683</v>
+        <v>0.756</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8811</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CERISUELO QUESADA</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.985</v>
+        <v>3.7398</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7663</v>
+        <v>2.5568</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7812</v>
+        <v>1.183</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9076</v>
+        <v>1.9471</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2324</v>
+        <v>-0.2894</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6752</v>
+        <v>2.2365</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0705</v>
+        <v>2.0593</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6291</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5586</v>
+        <v>1.2857</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1629</v>
+        <v>-0.1123</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3967</v>
+        <v>-1.0631</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2338</v>
+        <v>0.9508</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>0.899</v>
+        <v>-0.2579</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4223</v>
+        <v>-0.0357</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4767</v>
+        <v>-0.2222</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4074</v>
+        <v>0.2666</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2734</v>
+        <v>0.5331</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6808</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>J. CERISUELO QUESADA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8582</v>
+        <v>3.0928</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8437</v>
+        <v>3.7663</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0145</v>
+        <v>-0.6735</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9471</v>
+        <v>0.9076</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2894</v>
+        <v>0.2324</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2365</v>
+        <v>0.6752</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0593</v>
+        <v>1.0705</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7737000000000001</v>
+        <v>1.6291</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2857</v>
+        <v>-0.5586</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1123</v>
+        <v>-0.1629</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0631</v>
+        <v>-1.3967</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9508</v>
+        <v>1.2338</v>
       </c>
       <c r="P17" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1394</v>
+        <v>1.0067</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7488</v>
+        <v>0.4223</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3907</v>
+        <v>0.5844</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2666</v>
+        <v>-0.4074</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5331</v>
+        <v>2.2734</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1415</v>
+        <v>2.2888</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4591</v>
+        <v>1.2741</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6824</v>
+        <v>1.0148</v>
       </c>
       <c r="G18" t="n">
         <v>0.8063</v>
@@ -1858,13 +1858,13 @@
         <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7243000000000001</v>
+        <v>0.4231</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9984</v>
+        <v>-0.1834</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2741</v>
+        <v>0.6065</v>
       </c>
       <c r="V18" t="n">
         <v>0.2666</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5849</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9917</v>
+        <v>-0.4823</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4068</v>
+        <v>0.491</v>
       </c>
       <c r="G19" t="n">
         <v>0.016</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3902</v>
+        <v>0.9838</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0552</v>
+        <v>0.5645</v>
       </c>
       <c r="U19" t="n">
-        <v>0.335</v>
+        <v>0.4193</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3957</v>
+        <v>-1.22</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8734</v>
+        <v>1.0771</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2691</v>
+        <v>-2.2972</v>
       </c>
       <c r="G20" t="n">
         <v>0.4455</v>
@@ -2014,13 +2014,13 @@
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2793</v>
+        <v>-0.1037</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1574</v>
+        <v>0.1294</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7512</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5552</v>
+        <v>-1.5036</v>
       </c>
       <c r="E21" t="n">
         <v>-1.88</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3248</v>
+        <v>0.3764</v>
       </c>
       <c r="G21" t="n">
         <v>0.7668</v>
@@ -2092,13 +2092,13 @@
         <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.203</v>
+        <v>-0.1514</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1872</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0158</v>
+        <v>0.0358</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5331</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3004</v>
+        <v>-2.0156</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1424</v>
+        <v>-1.633</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.158</v>
+        <v>-0.3826</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9112</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0667</v>
+        <v>0.3515</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.312</v>
+        <v>0.1974</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3787</v>
+        <v>0.1541</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6633</v>
+        <v>-5.4558</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.76</v>
+        <v>-5.473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0172</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6585</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0458</v>
+        <v>0.2533</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5471</v>
+        <v>-0.166</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4987</v>
+        <v>0.4193</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8701</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.9582</v>
+        <v>2.9528</v>
       </c>
       <c r="E24" t="n">
-        <v>4.383900000000001</v>
+        <v>4.078500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4257</v>
+        <v>-1.1258</v>
       </c>
       <c r="G24" t="n">
         <v>3.849399999999999</v>
@@ -2296,7 +2296,7 @@
         <v>2.5771</v>
       </c>
       <c r="I24" t="n">
-        <v>1.2725</v>
+        <v>1.272500000000001</v>
       </c>
       <c r="J24" t="n">
         <v>11.8426</v>
@@ -2326,19 +2326,19 @@
         <v>12.6862</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4924</v>
+        <v>4.4868</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9098</v>
+        <v>1.6043</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5824</v>
+        <v>2.8826</v>
       </c>
       <c r="V24" t="n">
         <v>-6.1763</v>
       </c>
       <c r="W24" t="n">
-        <v>2.524900000000001</v>
+        <v>2.5249</v>
       </c>
       <c r="X24" t="n">
         <v>-8.7013</v>
